--- a/data/FANT26_schedule.xlsx
+++ b/data/FANT26_schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD518AA-63F4-4338-942A-153FACDB8BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0C61BE-E026-4180-AB67-E4C703D684D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3366" yWindow="1332" windowWidth="17280" windowHeight="9990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="9984" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presentors" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>Time</t>
   </si>
@@ -58,12 +58,6 @@
     <t>BOLAJI</t>
   </si>
   <si>
-    <t>Obeng Mensah &amp; Fäder</t>
-  </si>
-  <si>
-    <t>Deborah &amp; Eymard</t>
-  </si>
-  <si>
     <t>Musa</t>
   </si>
   <si>
@@ -152,6 +146,21 @@
   </si>
   <si>
     <t>End/ Beergarden</t>
+  </si>
+  <si>
+    <t>New archaeological fieldwork in the Tagant, Mauritania: The end of the Tichitt tradition?</t>
+  </si>
+  <si>
+    <t>Provenance analysis of clay smoking pipes in West Africa using pXRF</t>
+  </si>
+  <si>
+    <t>Juan-Marco</t>
+  </si>
+  <si>
+    <t>Sonja</t>
+  </si>
+  <si>
+    <t>Obeng Mensah, Deborah &amp; Fäder, Eymard</t>
   </si>
 </sst>
 </file>
@@ -490,7 +499,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -504,49 +513,52 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -557,24 +569,24 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -585,54 +597,60 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -648,7 +666,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -656,7 +674,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1">
         <v>0.41666666666666669</v>
@@ -664,7 +682,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1">
         <v>0.4375</v>
@@ -672,7 +690,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1">
         <v>0.5</v>
@@ -680,7 +698,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1">
         <v>0.5625</v>
@@ -688,7 +706,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B6" s="1">
         <v>0.64583333333333337</v>
@@ -696,15 +714,15 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1">
         <v>0.72916666666666663</v>
@@ -712,7 +730,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1">
         <v>0.76041666666666663</v>

--- a/data/FANT26_schedule.xlsx
+++ b/data/FANT26_schedule.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0C61BE-E026-4180-AB67-E4C703D684D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBB0C23-2FAD-4B20-910D-BDEE2655EDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="9984" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presentors" sheetId="1" r:id="rId1"/>
     <sheet name="Schedule" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
   <si>
     <t>Time</t>
   </si>
@@ -161,6 +162,18 @@
   </si>
   <si>
     <t>Obeng Mensah, Deborah &amp; Fäder, Eymard</t>
+  </si>
+  <si>
+    <t>Höhn</t>
+  </si>
+  <si>
+    <t>Alexa</t>
+  </si>
+  <si>
+    <t>Die archäobotanischen Vergleichssammlungen an der Goethe-Universität, Frankfurt am Main</t>
+  </si>
+  <si>
+    <t>Trans-Sudanic vs. Trans-Saharan contacts: chemical analysis of glass beads from Kanem, Chad</t>
   </si>
 </sst>
 </file>
@@ -485,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -605,10 +618,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>36</v>
@@ -616,10 +632,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
       </c>
       <c r="D10" t="s">
         <v>36</v>
@@ -627,13 +643,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
         <v>36</v>
@@ -641,15 +657,29 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>23</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>36</v>
       </c>
     </row>

--- a/data/FANT26_schedule.xlsx
+++ b/data/FANT26_schedule.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBB0C23-2FAD-4B20-910D-BDEE2655EDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC488EC-9A56-46AE-8599-4503E20CD6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presentors" sheetId="1" r:id="rId1"/>
     <sheet name="Schedule" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
   <si>
     <t>Time</t>
   </si>
@@ -174,6 +173,21 @@
   </si>
   <si>
     <t>Trans-Sudanic vs. Trans-Saharan contacts: chemical analysis of glass beads from Kanem, Chad</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>Adding value to medieval ceramic collections from Sudan held in German museum collections</t>
+  </si>
+  <si>
+    <t>Schulze</t>
+  </si>
+  <si>
+    <t>Maximilian</t>
   </si>
 </sst>
 </file>
@@ -498,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -520,13 +534,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -534,13 +548,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -548,13 +562,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -562,41 +576,41 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
         <v>35</v>
@@ -604,13 +618,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
@@ -618,52 +629,52 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>36</v>
@@ -671,15 +682,43 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>23</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -723,7 +762,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="1">
-        <v>0.5</v>
+        <v>0.50694444444444442</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -731,7 +770,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>0.5625</v>
+        <v>0.56944444444444442</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -739,7 +778,7 @@
         <v>37</v>
       </c>
       <c r="B6" s="1">
-        <v>0.64583333333333337</v>
+        <v>0.63888888888888884</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -747,7 +786,7 @@
         <v>36</v>
       </c>
       <c r="B7" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.65972222222222221</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">

--- a/data/FANT26_schedule.xlsx
+++ b/data/FANT26_schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC488EC-9A56-46AE-8599-4503E20CD6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AEAFFA-47DB-4C86-9E68-C7AC7282A04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presentors" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
   <si>
     <t>Time</t>
   </si>
@@ -188,6 +188,9 @@
   </si>
   <si>
     <t>Maximilian</t>
+  </si>
+  <si>
+    <t>Wrap-up</t>
   </si>
 </sst>
 </file>
@@ -548,13 +551,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -562,13 +565,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -576,13 +579,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -590,13 +593,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -629,13 +629,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -657,13 +657,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
         <v>35</v>
@@ -671,10 +671,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>36</v>
@@ -730,7 +733,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD60AE77-0982-4269-9292-019F7B0177A6}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -794,14 +797,22 @@
         <v>38</v>
       </c>
       <c r="B8" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.71527777777777779</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>0.76041666666666663</v>
       </c>
     </row>

--- a/data/FANT26_schedule.xlsx
+++ b/data/FANT26_schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AEAFFA-47DB-4C86-9E68-C7AC7282A04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2274CC-18CA-419A-B9ED-D51269162731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presentors" sheetId="1" r:id="rId1"/>
@@ -593,10 +593,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -671,13 +674,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>36</v>
